--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_216_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_216_R22.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2588</v>
+        <v>3.7765</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4161</v>
+        <v>5.2725</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1573</v>
+        <v>-1.496</v>
       </c>
       <c r="G2" t="n">
-        <v>1.169</v>
+        <v>7.3502</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0924</v>
+        <v>2.0169</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9234</v>
+        <v>5.3333</v>
       </c>
       <c r="J2" t="n">
-        <v>2.688</v>
+        <v>8.533899999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5039</v>
+        <v>2.672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.184</v>
+        <v>5.8619</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.519</v>
+        <v>-1.1837</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4116</v>
+        <v>-0.6551</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1074</v>
+        <v>-0.5286</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.9432</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4145</v>
+        <v>-0.8109</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3724</v>
+        <v>0.1456</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0422</v>
+        <v>-0.9566</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2836</v>
+        <v>0.2525</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3558</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3754</v>
+        <v>3.1882</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2411</v>
+        <v>4.5472</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8657</v>
+        <v>-1.3589</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3502</v>
+        <v>1.169</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0169</v>
+        <v>2.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3333</v>
+        <v>-0.9234</v>
       </c>
       <c r="J3" t="n">
-        <v>8.533899999999999</v>
+        <v>2.688</v>
       </c>
       <c r="K3" t="n">
-        <v>2.672</v>
+        <v>2.5039</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8619</v>
+        <v>0.184</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1837</v>
+        <v>-1.519</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6551</v>
+        <v>-0.4116</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5286</v>
+        <v>-1.1074</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9432</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.212</v>
+        <v>0.344</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1142</v>
+        <v>0.5034</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3262</v>
+        <v>-0.1595</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2525</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8307</v>
+        <v>2.1914</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3809</v>
+        <v>1.5735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4498</v>
+        <v>0.6179</v>
       </c>
       <c r="G4" t="n">
         <v>1.9427</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.112</v>
+        <v>0.2486</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2478</v>
+        <v>0.4404</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4068</v>
+        <v>1.9526</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8174</v>
+        <v>4.128</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4106</v>
+        <v>-2.1754</v>
       </c>
       <c r="G5" t="n">
         <v>3.0718</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9871</v>
+        <v>-0.4413</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1177</v>
+        <v>0.1928</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8694</v>
+        <v>-0.6341</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6778999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3008</v>
+        <v>-0.1343</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2938</v>
+        <v>1.5611</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5946</v>
+        <v>-1.6954</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2486</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7121</v>
+        <v>-0.5456</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0474</v>
+        <v>0.3148</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7595</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.3558</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4502</v>
+        <v>-0.2844</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7422</v>
+        <v>0.7736</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1924</v>
+        <v>-1.058</v>
       </c>
       <c r="G7" t="n">
         <v>0.3262</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9208</v>
+        <v>-0.7549</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1889</v>
+        <v>0.2203</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1097</v>
+        <v>-0.9752</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8787</v>
+        <v>-1.551</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9931</v>
+        <v>1.4216</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8718</v>
+        <v>-2.9726</v>
       </c>
       <c r="G8" t="n">
         <v>0.8924</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2324</v>
+        <v>0.0953</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0431</v>
+        <v>0.3855</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1893</v>
+        <v>-0.2902</v>
       </c>
       <c r="V8" t="n">
         <v>-2.5387</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4989</v>
+        <v>-3.5989</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4683</v>
+        <v>-2.518</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0306</v>
+        <v>-1.0809</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9243</v>
+        <v>-3.6845</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5327</v>
+        <v>-1.0143</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3915</v>
+        <v>-2.6702</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3797</v>
+        <v>-2.8837</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3627</v>
+        <v>-0.6351</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.017</v>
+        <v>-2.2486</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5446</v>
+        <v>-0.8008</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.17</v>
+        <v>-0.3792</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3746</v>
+        <v>-0.4216</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1287</v>
+        <v>0.4619</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5351</v>
+        <v>0.3657</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5152</v>
+        <v>-4.1164</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.636</v>
+        <v>-1.716</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8793</v>
+        <v>-2.4003</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6845</v>
+        <v>-1.9243</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0143</v>
+        <v>-1.5327</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6702</v>
+        <v>-0.3915</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8837</v>
+        <v>-0.3797</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6351</v>
+        <v>-0.3627</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2486</v>
+        <v>-0.017</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8008</v>
+        <v>-1.5446</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3792</v>
+        <v>-1.17</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4216</v>
+        <v>-0.3746</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5456</v>
+        <v>-0.7461</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2478</v>
+        <v>0.2873</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2978</v>
+        <v>-1.0334</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2843</v>
+        <v>-5.36</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9158</v>
+        <v>-1.0588</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3685</v>
+        <v>-4.3012</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0709</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3731</v>
+        <v>-1.4488</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0376</v>
+        <v>-0.1806</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3355</v>
+        <v>-1.2682</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0564</v>
+        <v>-3.936299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8645</v>
+        <v>13.9847</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.921</v>
+        <v>-17.9208</v>
       </c>
       <c r="G12" t="n">
-        <v>7.824</v>
+        <v>7.823999999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>2.035700000000001</v>
+        <v>2.0357</v>
       </c>
       <c r="I12" t="n">
-        <v>5.788200000000001</v>
+        <v>5.788200000000002</v>
       </c>
       <c r="J12" t="n">
         <v>19.551</v>
@@ -1378,7 +1378,7 @@
         <v>-7.7462</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.9809</v>
+        <v>-3.980900000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.4794</v>
@@ -1390,10 +1390,10 @@
         <v>10.438</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7181</v>
+        <v>-3.5978</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5552</v>
+        <v>2.6752</v>
       </c>
       <c r="U12" t="n">
         <v>-6.2732</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3289</v>
+        <v>4.5363</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7711</v>
+        <v>4.1814</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4422</v>
+        <v>0.3549</v>
       </c>
       <c r="G13" t="n">
         <v>1.1005</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6743</v>
+        <v>0.8817</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2151</v>
+        <v>0.6253</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5407999999999999</v>
+        <v>0.2563</v>
       </c>
       <c r="V13" t="n">
         <v>0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4446</v>
+        <v>3.6076</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0977</v>
+        <v>4.9797</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6531</v>
+        <v>-1.3722</v>
       </c>
       <c r="G14" t="n">
         <v>2.8379</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3747</v>
+        <v>0.5377</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0461</v>
+        <v>0.2348</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2656</v>
+        <v>2.7314</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6523</v>
+        <v>5.4677</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3867</v>
+        <v>-2.7364</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0103</v>
+        <v>-2.1653</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2977</v>
+        <v>-1.359</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7126</v>
+        <v>-0.8063</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9268999999999999</v>
+        <v>1.6374</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7429</v>
+        <v>0.2289</v>
       </c>
       <c r="L15" t="n">
-        <v>0.184</v>
+        <v>1.4085</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9373</v>
+        <v>-3.8027</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0406</v>
+        <v>-1.5879</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8966</v>
+        <v>-2.2148</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2072</v>
+        <v>0.8456</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4648</v>
+        <v>0.1206</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.5387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7501</v>
+        <v>3.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0801</v>
+        <v>2.5966</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2318</v>
+        <v>3.5343</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1517</v>
+        <v>-0.9377</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1653</v>
+        <v>-1.0103</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.359</v>
+        <v>-0.2977</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8063</v>
+        <v>-0.7126</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6374</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2289</v>
+        <v>0.7429</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4085</v>
+        <v>0.184</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8027</v>
+        <v>-1.9373</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5879</v>
+        <v>-1.0406</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2148</v>
+        <v>-0.8966</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.315</v>
+        <v>1.0734</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6097</v>
+        <v>1.0892</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2948</v>
+        <v>-0.0158</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5387</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2166</v>
+        <v>1.7501</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4915</v>
+        <v>1.9862</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4859</v>
+        <v>2.9013</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9944</v>
+        <v>-0.9151</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0853</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5856</v>
+        <v>0.9091</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8136</v>
+        <v>0.6018</v>
       </c>
       <c r="U17" t="n">
-        <v>0.228</v>
+        <v>0.3073</v>
       </c>
       <c r="V17" t="n">
         <v>0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.065</v>
+        <v>0.8006</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1222</v>
+        <v>0.4761</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0572</v>
+        <v>0.3245</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5263</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3365</v>
+        <v>0.3991</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1415</v>
+        <v>0.2124</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.195</v>
+        <v>0.1867</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2311</v>
+        <v>-0.5292</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0609</v>
+        <v>0.0791</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2921</v>
+        <v>-0.6083</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7498</v>
+        <v>-1.005</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2673</v>
+        <v>-0.2689</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0171</v>
+        <v>-0.7361</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0023</v>
+        <v>0.0672</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6979</v>
+        <v>0.0672</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3044</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7521</v>
+        <v>-1.0722</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4306</v>
+        <v>-0.3361</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3215</v>
+        <v>-0.7361</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7506</v>
+        <v>0.0119</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3961</v>
+        <v>0.0119</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3545</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7651</v>
+        <v>-0.7581</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1568</v>
+        <v>1.5891</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6083</v>
+        <v>-2.3472</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.005</v>
+        <v>-0.7498</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2689</v>
+        <v>0.2673</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7361</v>
+        <v>-1.0171</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0672</v>
+        <v>2.0023</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0672</v>
+        <v>1.6979</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.3044</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0722</v>
+        <v>-2.7521</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3361</v>
+        <v>-1.4306</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7361</v>
+        <v>-1.3215</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.224</v>
+        <v>1.2237</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.224</v>
+        <v>0.9243</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.2994</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1883</v>
+        <v>-0.8116</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6403</v>
+        <v>-0.7582</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.548</v>
+        <v>-0.0534</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0728</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0622</v>
+        <v>1.4389</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2151</v>
+        <v>1.0971</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1529</v>
+        <v>0.3418</v>
       </c>
       <c r="V21" t="n">
         <v>0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2491</v>
+        <v>-2.1991</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0375</v>
+        <v>-1.1555</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2116</v>
+        <v>-1.0436</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8384</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0532</v>
+        <v>0.1032</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2104</v>
+        <v>-0.0424</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1854</v>
+        <v>-3.7586</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6663</v>
+        <v>-3.374</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5191</v>
+        <v>-0.3846</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3091</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8918</v>
+        <v>0.3185</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1246</v>
+        <v>0.4169</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2328</v>
+        <v>-0.0984</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.056699999999999</v>
+        <v>8.2021</v>
       </c>
       <c r="E24" t="n">
         <v>17.921</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.8644</v>
+        <v>-9.719100000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-7.8239</v>
@@ -2326,13 +2326,13 @@
         <v>13.9173</v>
       </c>
       <c r="S24" t="n">
-        <v>4.7181</v>
+        <v>7.863400000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>6.2731</v>
+        <v>6.273000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5551</v>
+        <v>1.5903</v>
       </c>
       <c r="V24" t="n">
         <v>4.6831</v>
